--- a/templates/2_到发站对表模板.xlsx
+++ b/templates/2_到发站对表模板.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="484">
   <si>
     <t>出发站</t>
   </si>
@@ -35,223 +35,1450 @@
     <t>到达站</t>
   </si>
   <si>
+    <t>范围</t>
+  </si>
+  <si>
+    <t>0~0</t>
+  </si>
+  <si>
+    <t>鄱阳</t>
+  </si>
+  <si>
+    <t>友好</t>
+  </si>
+  <si>
+    <t>当阳</t>
+  </si>
+  <si>
+    <t>沙沱</t>
+  </si>
+  <si>
+    <t>五道河</t>
+  </si>
+  <si>
+    <t>涵江</t>
+  </si>
+  <si>
+    <t>旅顺</t>
+  </si>
+  <si>
+    <t>南堡北</t>
+  </si>
+  <si>
+    <t>清河西</t>
+  </si>
+  <si>
+    <t>三明北</t>
+  </si>
+  <si>
+    <t>营街</t>
+  </si>
+  <si>
+    <t>麻涌</t>
+  </si>
+  <si>
+    <t>泾川</t>
+  </si>
+  <si>
+    <t>张桥</t>
+  </si>
+  <si>
+    <t>大杖子</t>
+  </si>
+  <si>
+    <t>塔崖驿</t>
+  </si>
+  <si>
+    <t>宜城南</t>
+  </si>
+  <si>
+    <t>密云北</t>
+  </si>
+  <si>
+    <t>茂名南</t>
+  </si>
+  <si>
+    <t>灵宝</t>
+  </si>
+  <si>
+    <t>兴宁</t>
+  </si>
+  <si>
+    <t>余姚</t>
+  </si>
+  <si>
+    <t>深圳机场</t>
+  </si>
+  <si>
+    <t>后湖</t>
+  </si>
+  <si>
+    <t>莒县</t>
+  </si>
+  <si>
+    <t>白银南</t>
+  </si>
+  <si>
+    <t>长乐东</t>
+  </si>
+  <si>
+    <t>含山南</t>
+  </si>
+  <si>
+    <t>渠县</t>
+  </si>
+  <si>
+    <t>武清</t>
+  </si>
+  <si>
+    <t>蔡家坡</t>
+  </si>
+  <si>
+    <t>南丹</t>
+  </si>
+  <si>
+    <t>建瓯西</t>
+  </si>
+  <si>
+    <t>桂平</t>
+  </si>
+  <si>
+    <t>新绛</t>
+  </si>
+  <si>
+    <t>亳州南</t>
+  </si>
+  <si>
+    <t>阳泉</t>
+  </si>
+  <si>
+    <t>尚志</t>
+  </si>
+  <si>
+    <t>阿勒泰</t>
+  </si>
+  <si>
+    <t>太平川</t>
+  </si>
+  <si>
+    <t>蔡山</t>
+  </si>
+  <si>
+    <t>灵宝西</t>
+  </si>
+  <si>
+    <t>加格达奇</t>
+  </si>
+  <si>
+    <t>新乡东</t>
+  </si>
+  <si>
+    <t>汤原</t>
+  </si>
+  <si>
+    <t>双城堡</t>
+  </si>
+  <si>
+    <t>昆玉</t>
+  </si>
+  <si>
+    <t>伊春西</t>
+  </si>
+  <si>
+    <t>延平东</t>
+  </si>
+  <si>
+    <t>三岔湖</t>
+  </si>
+  <si>
+    <t>莱西南</t>
+  </si>
+  <si>
+    <t>邛崃</t>
+  </si>
+  <si>
+    <t>长宁</t>
+  </si>
+  <si>
+    <t>若羌</t>
+  </si>
+  <si>
+    <t>宁波东</t>
+  </si>
+  <si>
+    <t>清河城</t>
+  </si>
+  <si>
+    <t>淮安东</t>
+  </si>
+  <si>
+    <t>简阳南</t>
+  </si>
+  <si>
+    <t>丰城南</t>
+  </si>
+  <si>
+    <t>庄寨</t>
+  </si>
+  <si>
+    <t>深圳北</t>
+  </si>
+  <si>
+    <t>昌黎</t>
+  </si>
+  <si>
+    <t>楚雄</t>
+  </si>
+  <si>
+    <t>井陉</t>
+  </si>
+  <si>
+    <t>纳堆</t>
+  </si>
+  <si>
+    <t>乐山</t>
+  </si>
+  <si>
+    <t>银川</t>
+  </si>
+  <si>
+    <t>庙庄</t>
+  </si>
+  <si>
+    <t>上海西</t>
+  </si>
+  <si>
+    <t>那曲</t>
+  </si>
+  <si>
+    <t>新宾</t>
+  </si>
+  <si>
+    <t>沙河市</t>
+  </si>
+  <si>
+    <t>桃村北</t>
+  </si>
+  <si>
+    <t>独山东</t>
+  </si>
+  <si>
+    <t>惠州北</t>
+  </si>
+  <si>
+    <t>龙泉寺</t>
+  </si>
+  <si>
+    <t>辽中</t>
+  </si>
+  <si>
+    <t>奎屯</t>
+  </si>
+  <si>
+    <t>宝林</t>
+  </si>
+  <si>
+    <t>张家港</t>
+  </si>
+  <si>
+    <t>东乡</t>
+  </si>
+  <si>
+    <t>毛坝关</t>
+  </si>
+  <si>
+    <t>大涧</t>
+  </si>
+  <si>
+    <t>滕州</t>
+  </si>
+  <si>
+    <t>六枝南</t>
+  </si>
+  <si>
+    <t>邵阳西</t>
+  </si>
+  <si>
+    <t>龙洞</t>
+  </si>
+  <si>
+    <t>辛集</t>
+  </si>
+  <si>
+    <t>洪洞西</t>
+  </si>
+  <si>
+    <t>咸阳北</t>
+  </si>
+  <si>
+    <t>老莱</t>
+  </si>
+  <si>
+    <t>郏县</t>
+  </si>
+  <si>
+    <t>开原西</t>
+  </si>
+  <si>
+    <t>本溪</t>
+  </si>
+  <si>
+    <t>资中西</t>
+  </si>
+  <si>
+    <t>东胜东</t>
+  </si>
+  <si>
+    <t>周家</t>
+  </si>
+  <si>
+    <t>宜兴</t>
+  </si>
+  <si>
+    <t>龙丰</t>
+  </si>
+  <si>
+    <t>邳州东</t>
+  </si>
+  <si>
+    <t>宾阳</t>
+  </si>
+  <si>
+    <t>岗嘎</t>
+  </si>
+  <si>
+    <t>库尔勒</t>
+  </si>
+  <si>
+    <t>耒阳</t>
+  </si>
+  <si>
+    <t>遂溪</t>
+  </si>
+  <si>
+    <t>梅州西</t>
+  </si>
+  <si>
+    <t>耒阳西</t>
+  </si>
+  <si>
+    <t>小雨谷</t>
+  </si>
+  <si>
+    <t>尤溪</t>
+  </si>
+  <si>
+    <t>创业村</t>
+  </si>
+  <si>
+    <t>王瞳</t>
+  </si>
+  <si>
+    <t>义县</t>
+  </si>
+  <si>
+    <t>南朗</t>
+  </si>
+  <si>
+    <t>阿南庄</t>
+  </si>
+  <si>
+    <t>小东</t>
+  </si>
+  <si>
+    <t>疏勒河</t>
+  </si>
+  <si>
+    <t>准东</t>
+  </si>
+  <si>
+    <t>雨格</t>
+  </si>
+  <si>
+    <t>马莲河</t>
+  </si>
+  <si>
+    <t>甘泉</t>
+  </si>
+  <si>
+    <t>崖州湾</t>
+  </si>
+  <si>
+    <t>南靖</t>
+  </si>
+  <si>
+    <t>永寿</t>
+  </si>
+  <si>
+    <t>宿迁</t>
+  </si>
+  <si>
+    <t>桃村</t>
+  </si>
+  <si>
+    <t>前苇塘</t>
+  </si>
+  <si>
+    <t>侯马西</t>
+  </si>
+  <si>
+    <t>铜川</t>
+  </si>
+  <si>
+    <t>金山</t>
+  </si>
+  <si>
+    <t>临澧西</t>
+  </si>
+  <si>
+    <t>温州南</t>
+  </si>
+  <si>
+    <t>香坊</t>
+  </si>
+  <si>
+    <t>锡林浩特</t>
+  </si>
+  <si>
+    <t>晋州</t>
+  </si>
+  <si>
+    <t>沙岭子</t>
+  </si>
+  <si>
+    <t>桐梓北</t>
+  </si>
+  <si>
+    <t>张百湾</t>
+  </si>
+  <si>
+    <t>南宫东</t>
+  </si>
+  <si>
+    <t>三营</t>
+  </si>
+  <si>
+    <t>青白江东</t>
+  </si>
+  <si>
+    <t>浮梁东</t>
+  </si>
+  <si>
+    <t>六合</t>
+  </si>
+  <si>
+    <t>梅河口</t>
+  </si>
+  <si>
+    <t>三家寨</t>
+  </si>
+  <si>
+    <t>彰武</t>
+  </si>
+  <si>
+    <t>江宁西</t>
+  </si>
+  <si>
+    <t>如皋南</t>
+  </si>
+  <si>
+    <t>东莞</t>
+  </si>
+  <si>
+    <t>小湾东</t>
+  </si>
+  <si>
+    <t>五河</t>
+  </si>
+  <si>
+    <t>免渡河</t>
+  </si>
+  <si>
+    <t>丹东西</t>
+  </si>
+  <si>
+    <t>那罗</t>
+  </si>
+  <si>
+    <t>阿尔山北</t>
+  </si>
+  <si>
+    <t>兴城西</t>
+  </si>
+  <si>
+    <t>根河</t>
+  </si>
+  <si>
+    <t>泰山</t>
+  </si>
+  <si>
+    <t>延庆</t>
+  </si>
+  <si>
+    <t>安图</t>
+  </si>
+  <si>
+    <t>昆山南</t>
+  </si>
+  <si>
+    <t>廊坊西</t>
+  </si>
+  <si>
+    <t>南宁北</t>
+  </si>
+  <si>
+    <t>邯郸</t>
+  </si>
+  <si>
+    <t>城阳</t>
+  </si>
+  <si>
+    <t>安图西</t>
+  </si>
+  <si>
+    <t>鹤庆</t>
+  </si>
+  <si>
+    <t>台安南</t>
+  </si>
+  <si>
+    <t>乌西</t>
+  </si>
+  <si>
+    <t>北京丰台</t>
+  </si>
+  <si>
+    <t>昆明南</t>
+  </si>
+  <si>
+    <t>额敏</t>
+  </si>
+  <si>
+    <t>巴楚</t>
+  </si>
+  <si>
+    <t>四方台</t>
+  </si>
+  <si>
+    <t>常山</t>
+  </si>
+  <si>
+    <t>广通北</t>
+  </si>
+  <si>
+    <t>明光</t>
+  </si>
+  <si>
+    <t>五女山</t>
+  </si>
+  <si>
+    <t>吴桥</t>
+  </si>
+  <si>
+    <t>衡阳东</t>
+  </si>
+  <si>
+    <t>巴林</t>
+  </si>
+  <si>
+    <t>美溪</t>
+  </si>
+  <si>
+    <t>丹江口</t>
+  </si>
+  <si>
+    <t>莒南北</t>
+  </si>
+  <si>
+    <t>金阳</t>
+  </si>
+  <si>
+    <t>磐安镇</t>
+  </si>
+  <si>
+    <t>桑园子</t>
+  </si>
+  <si>
+    <t>钟祥南</t>
+  </si>
+  <si>
+    <t>德惠西</t>
+  </si>
+  <si>
+    <t>温岭</t>
+  </si>
+  <si>
+    <t>任丘西</t>
+  </si>
+  <si>
+    <t>安泽</t>
+  </si>
+  <si>
+    <t>四平东</t>
+  </si>
+  <si>
+    <t>大王滩</t>
+  </si>
+  <si>
+    <t>安化</t>
+  </si>
+  <si>
+    <t>麻城</t>
+  </si>
+  <si>
+    <t>1~10</t>
+  </si>
+  <si>
+    <t>莱阳</t>
+  </si>
+  <si>
+    <t>永川南</t>
+  </si>
+  <si>
+    <t>平顶山西</t>
+  </si>
+  <si>
+    <t>天津西</t>
+  </si>
+  <si>
+    <t>汉中</t>
+  </si>
+  <si>
+    <t>西安东</t>
+  </si>
+  <si>
+    <t>延平西</t>
+  </si>
+  <si>
+    <t>嘉兴南</t>
+  </si>
+  <si>
+    <t>辽阳</t>
+  </si>
+  <si>
+    <t>莱州</t>
+  </si>
+  <si>
+    <t>北京西</t>
+  </si>
+  <si>
+    <t>庐江西</t>
+  </si>
+  <si>
+    <t>太原南</t>
+  </si>
+  <si>
+    <t>常州北</t>
+  </si>
+  <si>
+    <t>巴南</t>
+  </si>
+  <si>
+    <t>牛车河</t>
+  </si>
+  <si>
+    <t>濮阳东</t>
+  </si>
+  <si>
+    <t>东安东</t>
+  </si>
+  <si>
+    <t>吉安西</t>
+  </si>
+  <si>
+    <t>大冶北</t>
+  </si>
+  <si>
+    <t>郑州航空港</t>
+  </si>
+  <si>
+    <t>杭州</t>
+  </si>
+  <si>
+    <t>黄山北</t>
+  </si>
+  <si>
+    <t>德兴</t>
+  </si>
+  <si>
+    <t>汉口</t>
+  </si>
+  <si>
+    <t>盘州</t>
+  </si>
+  <si>
+    <t>桂林</t>
+  </si>
+  <si>
+    <t>南京南</t>
+  </si>
+  <si>
+    <t>十堰东</t>
+  </si>
+  <si>
+    <t>金寨</t>
+  </si>
+  <si>
+    <t>日照</t>
+  </si>
+  <si>
+    <t>萧县北</t>
+  </si>
+  <si>
+    <t>金华</t>
+  </si>
+  <si>
+    <t>弋阳</t>
+  </si>
+  <si>
+    <t>孝感东</t>
+  </si>
+  <si>
+    <t>巴东</t>
+  </si>
+  <si>
+    <t>黟县东</t>
+  </si>
+  <si>
+    <t>武穴北</t>
+  </si>
+  <si>
+    <t>安顺西</t>
+  </si>
+  <si>
+    <t>犍为</t>
+  </si>
+  <si>
+    <t>金华南</t>
+  </si>
+  <si>
+    <t>宜春</t>
+  </si>
+  <si>
+    <t>廊坊</t>
+  </si>
+  <si>
+    <t>邯郸东</t>
+  </si>
+  <si>
     <t>郑州东</t>
   </si>
   <si>
+    <t>临清东</t>
+  </si>
+  <si>
+    <t>汉川北</t>
+  </si>
+  <si>
+    <t>武夷山北</t>
+  </si>
+  <si>
+    <t>上海南</t>
+  </si>
+  <si>
+    <t>横店</t>
+  </si>
+  <si>
+    <t>汕头</t>
+  </si>
+  <si>
+    <t>扬州东</t>
+  </si>
+  <si>
+    <t>上海</t>
+  </si>
+  <si>
+    <t>太湖南</t>
+  </si>
+  <si>
+    <t>齐河</t>
+  </si>
+  <si>
+    <t>唐山</t>
+  </si>
+  <si>
+    <t>宝坻</t>
+  </si>
+  <si>
+    <t>北京通州</t>
+  </si>
+  <si>
+    <t>太仓</t>
+  </si>
+  <si>
+    <t>宁海</t>
+  </si>
+  <si>
+    <t>烟台</t>
+  </si>
+  <si>
+    <t>洋县西</t>
+  </si>
+  <si>
+    <t>长汀南</t>
+  </si>
+  <si>
+    <t>丰城东</t>
+  </si>
+  <si>
+    <t>济南西</t>
+  </si>
+  <si>
+    <t>民权北</t>
+  </si>
+  <si>
+    <t>重庆北</t>
+  </si>
+  <si>
+    <t>泸州</t>
+  </si>
+  <si>
+    <t>广宁</t>
+  </si>
+  <si>
+    <t>苍南</t>
+  </si>
+  <si>
+    <t>珠海</t>
+  </si>
+  <si>
+    <t>潮汕</t>
+  </si>
+  <si>
+    <t>白沙铺</t>
+  </si>
+  <si>
+    <t>台安</t>
+  </si>
+  <si>
+    <t>滑浚</t>
+  </si>
+  <si>
+    <t>沙洋西</t>
+  </si>
+  <si>
+    <t>保定东</t>
+  </si>
+  <si>
+    <t>铁岭西</t>
+  </si>
+  <si>
+    <t>济南东</t>
+  </si>
+  <si>
+    <t>日照西</t>
+  </si>
+  <si>
+    <t>平原东</t>
+  </si>
+  <si>
+    <t>霞浦</t>
+  </si>
+  <si>
+    <t>泰安</t>
+  </si>
+  <si>
+    <t>上饶</t>
+  </si>
+  <si>
+    <t>虎门</t>
+  </si>
+  <si>
+    <t>吉首东</t>
+  </si>
+  <si>
+    <t>北京南</t>
+  </si>
+  <si>
+    <t>扬州</t>
+  </si>
+  <si>
+    <t>安阳东</t>
+  </si>
+  <si>
+    <t>沈阳北</t>
+  </si>
+  <si>
+    <t>奉节</t>
+  </si>
+  <si>
+    <t>佛山西</t>
+  </si>
+  <si>
+    <t>南宁东</t>
+  </si>
+  <si>
+    <t>莆田</t>
+  </si>
+  <si>
+    <t>广州南</t>
+  </si>
+  <si>
+    <t>南昌</t>
+  </si>
+  <si>
+    <t>信丰西</t>
+  </si>
+  <si>
+    <t>齐齐哈尔南</t>
+  </si>
+  <si>
+    <t>南乐</t>
+  </si>
+  <si>
+    <t>潍坊北</t>
+  </si>
+  <si>
+    <t>南昌东</t>
+  </si>
+  <si>
+    <t>武陟</t>
+  </si>
+  <si>
+    <t>晋中</t>
+  </si>
+  <si>
+    <t>三门峡南</t>
+  </si>
+  <si>
+    <t>开化</t>
+  </si>
+  <si>
+    <t>保康县</t>
+  </si>
+  <si>
+    <t>方城</t>
+  </si>
+  <si>
+    <t>巨野北</t>
+  </si>
+  <si>
+    <t>德阳</t>
+  </si>
+  <si>
+    <t>桑植</t>
+  </si>
+  <si>
+    <t>张家界西</t>
+  </si>
+  <si>
+    <t>嵊州新昌</t>
+  </si>
+  <si>
+    <t>普宁</t>
+  </si>
+  <si>
+    <t>江阴</t>
+  </si>
+  <si>
+    <t>德州东</t>
+  </si>
+  <si>
+    <t>绩溪北</t>
+  </si>
+  <si>
+    <t>沧州西</t>
+  </si>
+  <si>
+    <t>阳澄湖</t>
+  </si>
+  <si>
+    <t>龙游</t>
+  </si>
+  <si>
+    <t>邵阳北</t>
+  </si>
+  <si>
+    <t>重庆西</t>
+  </si>
+  <si>
+    <t>兰州西</t>
+  </si>
+  <si>
+    <t>常德</t>
+  </si>
+  <si>
+    <t>古丈西</t>
+  </si>
+  <si>
+    <t>庆阳</t>
+  </si>
+  <si>
+    <t>邹平</t>
+  </si>
+  <si>
+    <t>济南</t>
+  </si>
+  <si>
+    <t>晋城东</t>
+  </si>
+  <si>
+    <t>漯河西</t>
+  </si>
+  <si>
+    <t>淄博北</t>
+  </si>
+  <si>
+    <t>六安</t>
+  </si>
+  <si>
+    <t>广德南</t>
+  </si>
+  <si>
+    <t>武汉</t>
+  </si>
+  <si>
+    <t>绍兴北</t>
+  </si>
+  <si>
+    <t>鄂州</t>
+  </si>
+  <si>
+    <t>漳州</t>
+  </si>
+  <si>
+    <t>福清西</t>
+  </si>
+  <si>
+    <t>淄博</t>
+  </si>
+  <si>
+    <t>茌平南</t>
+  </si>
+  <si>
+    <t>合肥北城</t>
+  </si>
+  <si>
+    <t>神农架</t>
+  </si>
+  <si>
+    <t>荆州</t>
+  </si>
+  <si>
+    <t>高邑西</t>
+  </si>
+  <si>
+    <t>全州南</t>
+  </si>
+  <si>
+    <t>谷城北</t>
+  </si>
+  <si>
+    <t>邢台东</t>
+  </si>
+  <si>
+    <t>赤壁北</t>
+  </si>
+  <si>
+    <t>新沂南</t>
+  </si>
+  <si>
+    <t>连云港</t>
+  </si>
+  <si>
+    <t>昌邑</t>
+  </si>
+  <si>
+    <t>莱西</t>
+  </si>
+  <si>
+    <t>天门</t>
+  </si>
+  <si>
+    <t>延平</t>
+  </si>
+  <si>
+    <t>淮南东</t>
+  </si>
+  <si>
+    <t>赣榆</t>
+  </si>
+  <si>
+    <t>萍乡北</t>
+  </si>
+  <si>
+    <t>宜昌北</t>
+  </si>
+  <si>
+    <t>桂林西</t>
+  </si>
+  <si>
+    <t>广州</t>
+  </si>
+  <si>
+    <t>葫芦岛北</t>
+  </si>
+  <si>
+    <t>蓬莱</t>
+  </si>
+  <si>
+    <t>10~40</t>
+  </si>
+  <si>
+    <t>海安</t>
+  </si>
+  <si>
+    <t>杭州西</t>
+  </si>
+  <si>
+    <t>岳阳东</t>
+  </si>
+  <si>
+    <t>湖州南浔</t>
+  </si>
+  <si>
+    <t>杭州东</t>
+  </si>
+  <si>
+    <t>苏州北</t>
+  </si>
+  <si>
+    <t>西安北</t>
+  </si>
+  <si>
+    <t>大兴机场</t>
+  </si>
+  <si>
+    <t>平度</t>
+  </si>
+  <si>
+    <t>桐乡</t>
+  </si>
+  <si>
+    <t>洛阳龙门</t>
+  </si>
+  <si>
+    <t>杨陵南</t>
+  </si>
+  <si>
+    <t>常熟</t>
+  </si>
+  <si>
+    <t>徐州东</t>
+  </si>
+  <si>
+    <t>南川北</t>
+  </si>
+  <si>
+    <t>重庆东</t>
+  </si>
+  <si>
+    <t>镇江南</t>
+  </si>
+  <si>
+    <t>砀山南</t>
+  </si>
+  <si>
+    <t>嘉善南</t>
+  </si>
+  <si>
+    <t>长沙南</t>
+  </si>
+  <si>
+    <t>驻马店西</t>
+  </si>
+  <si>
+    <t>永城北</t>
+  </si>
+  <si>
+    <t>开封北</t>
+  </si>
+  <si>
+    <t>万州北</t>
+  </si>
+  <si>
+    <t>诸暨</t>
+  </si>
+  <si>
+    <t>红安西</t>
+  </si>
+  <si>
+    <t>白洋淀</t>
+  </si>
+  <si>
+    <t>天水南</t>
+  </si>
+  <si>
+    <t>绵阳</t>
+  </si>
+  <si>
+    <t>襄阳东</t>
+  </si>
+  <si>
     <t>石家庄</t>
   </si>
   <si>
-    <t>武汉</t>
-  </si>
-  <si>
-    <t>邯郸东</t>
-  </si>
-  <si>
-    <t>广州南</t>
-  </si>
-  <si>
-    <t>长沙南</t>
-  </si>
-  <si>
-    <t>天津西</t>
-  </si>
-  <si>
-    <t>济南西</t>
-  </si>
-  <si>
-    <t>徐州东</t>
-  </si>
-  <si>
-    <t>南京南</t>
-  </si>
-  <si>
-    <t>杭州东</t>
+    <t>秦皇岛</t>
+  </si>
+  <si>
+    <t>上海虹桥</t>
+  </si>
+  <si>
+    <t>丹阳北</t>
+  </si>
+  <si>
+    <t>增城</t>
+  </si>
+  <si>
+    <t>惠州南</t>
+  </si>
+  <si>
+    <t>盘锦北</t>
+  </si>
+  <si>
+    <t>锦州南</t>
+  </si>
+  <si>
+    <t>祁东</t>
+  </si>
+  <si>
+    <t>随州南</t>
+  </si>
+  <si>
+    <t>武当山西</t>
+  </si>
+  <si>
+    <t>山海关</t>
+  </si>
+  <si>
+    <t>哈尔滨西</t>
+  </si>
+  <si>
+    <t>成都东</t>
+  </si>
+  <si>
+    <t>隆昌北</t>
+  </si>
+  <si>
+    <t>长春西</t>
+  </si>
+  <si>
+    <t>阳江北</t>
+  </si>
+  <si>
+    <t>吴川</t>
+  </si>
+  <si>
+    <t>鹰潭北</t>
+  </si>
+  <si>
+    <t>贵阳北</t>
+  </si>
+  <si>
+    <t>宣城</t>
+  </si>
+  <si>
+    <t>阜阳西</t>
+  </si>
+  <si>
+    <t>焦作</t>
+  </si>
+  <si>
+    <t>惠东</t>
+  </si>
+  <si>
+    <t>綦江东</t>
+  </si>
+  <si>
+    <t>枣庄</t>
+  </si>
+  <si>
+    <t>蚌埠南</t>
+  </si>
+  <si>
+    <t>贺州</t>
+  </si>
+  <si>
+    <t>桂林北</t>
+  </si>
+  <si>
+    <t>青岛西</t>
+  </si>
+  <si>
+    <t>曲阜东</t>
+  </si>
+  <si>
+    <t>眉山东</t>
+  </si>
+  <si>
+    <t>宿州东</t>
+  </si>
+  <si>
+    <t>兴山</t>
+  </si>
+  <si>
+    <t>台州</t>
+  </si>
+  <si>
+    <t>永州</t>
+  </si>
+  <si>
+    <t>广元</t>
+  </si>
+  <si>
+    <t>华山北</t>
+  </si>
+  <si>
+    <t>界首南</t>
+  </si>
+  <si>
+    <t>临泉</t>
+  </si>
+  <si>
+    <t>福州南</t>
+  </si>
+  <si>
+    <t>南平市</t>
+  </si>
+  <si>
+    <t>荆门西</t>
+  </si>
+  <si>
+    <t>韶关</t>
+  </si>
+  <si>
+    <t>清远</t>
+  </si>
+  <si>
+    <t>厦门北</t>
+  </si>
+  <si>
+    <t>泉州东</t>
+  </si>
+  <si>
+    <t>厦门</t>
+  </si>
+  <si>
+    <t>怀化南</t>
+  </si>
+  <si>
+    <t>新化南</t>
+  </si>
+  <si>
+    <t>宁国南</t>
+  </si>
+  <si>
+    <t>义乌</t>
+  </si>
+  <si>
+    <t>丽水</t>
+  </si>
+  <si>
+    <t>兰考南</t>
+  </si>
+  <si>
+    <t>商丘</t>
+  </si>
+  <si>
+    <t>哈尔滨</t>
+  </si>
+  <si>
+    <t>江油</t>
+  </si>
+  <si>
+    <t>安陆西</t>
+  </si>
+  <si>
+    <t>娄底南</t>
+  </si>
+  <si>
+    <t>醴陵东</t>
+  </si>
+  <si>
+    <t>许昌东</t>
   </si>
   <si>
     <t>合肥南</t>
   </si>
   <si>
-    <t>襄阳东</t>
-  </si>
-  <si>
-    <t>重庆</t>
+    <t>镇江</t>
+  </si>
+  <si>
+    <t>临沂北</t>
+  </si>
+  <si>
+    <t>禹州</t>
+  </si>
+  <si>
+    <t>南阳东</t>
+  </si>
+  <si>
+    <t>绥中北</t>
+  </si>
+  <si>
+    <t>光明城</t>
+  </si>
+  <si>
+    <t>当阳西</t>
+  </si>
+  <si>
+    <t>孝感北</t>
+  </si>
+  <si>
+    <t>信阳东</t>
+  </si>
+  <si>
+    <t>40~60</t>
+  </si>
+  <si>
+    <t>郴州西</t>
+  </si>
+  <si>
+    <t>鹤壁东</t>
+  </si>
+  <si>
+    <t>福州</t>
+  </si>
+  <si>
+    <t>遵义</t>
+  </si>
+  <si>
+    <t>曲靖北</t>
+  </si>
+  <si>
+    <t>常州</t>
+  </si>
+  <si>
+    <t>咸宁北</t>
+  </si>
+  <si>
+    <t>内江北</t>
   </si>
   <si>
     <t>南昌西</t>
   </si>
   <si>
-    <t>怀化南</t>
-  </si>
-  <si>
-    <t>贵阳东</t>
-  </si>
-  <si>
-    <t>秦皇岛</t>
-  </si>
-  <si>
-    <t>沈阳北</t>
-  </si>
-  <si>
-    <t>哈尔滨西</t>
-  </si>
-  <si>
-    <t>商丘</t>
-  </si>
-  <si>
-    <t>西安北</t>
-  </si>
-  <si>
-    <t>德州东</t>
-  </si>
-  <si>
-    <t>枣庄</t>
-  </si>
-  <si>
-    <t>宿迁</t>
-  </si>
-  <si>
-    <t>淮安东</t>
-  </si>
-  <si>
-    <t>沧州西</t>
-  </si>
-  <si>
-    <t>廊坊</t>
-  </si>
-  <si>
-    <t>蚌埠南</t>
-  </si>
-  <si>
-    <t>德阳</t>
-  </si>
-  <si>
-    <t>广元</t>
-  </si>
-  <si>
-    <t>汉中</t>
-  </si>
-  <si>
-    <t>洛阳龙门</t>
-  </si>
-  <si>
-    <t>盐城</t>
-  </si>
-  <si>
-    <t>开封北</t>
-  </si>
-  <si>
-    <t>保定东</t>
-  </si>
-  <si>
-    <t>新乡东</t>
-  </si>
-  <si>
-    <t>株洲西</t>
-  </si>
-  <si>
-    <t>耒阳西</t>
-  </si>
-  <si>
-    <t>衡阳东</t>
-  </si>
-  <si>
-    <t>安阳东</t>
-  </si>
-  <si>
-    <t>兰考南</t>
-  </si>
-  <si>
-    <t>宝鸡南</t>
-  </si>
-  <si>
-    <t>天水南</t>
-  </si>
-  <si>
-    <t>华山北</t>
-  </si>
-  <si>
-    <t>苏州北</t>
-  </si>
-  <si>
-    <t>昆山南</t>
+    <t>余姚北</t>
+  </si>
+  <si>
+    <t>衢州</t>
+  </si>
+  <si>
+    <t>溧水</t>
+  </si>
+  <si>
+    <t>60~100</t>
   </si>
   <si>
     <t>无锡</t>
   </si>
   <si>
-    <t>镇江</t>
-  </si>
-  <si>
-    <t>六安</t>
-  </si>
-  <si>
-    <t>常州北</t>
-  </si>
-  <si>
-    <t>岳阳东</t>
-  </si>
-  <si>
-    <t>贵阳北</t>
-  </si>
-  <si>
-    <t>黄山北</t>
-  </si>
-  <si>
-    <t>汉口</t>
-  </si>
-  <si>
-    <t>嘉兴南</t>
-  </si>
-  <si>
-    <t>赣州西</t>
-  </si>
-  <si>
-    <t>潍坊</t>
-  </si>
-  <si>
-    <t>韶关</t>
-  </si>
-  <si>
-    <t>菏泽东</t>
-  </si>
-  <si>
-    <t>桂林西</t>
-  </si>
-  <si>
-    <t>枣阳</t>
-  </si>
-  <si>
-    <t>宜昌北</t>
-  </si>
-  <si>
-    <t>马鞍山东</t>
-  </si>
-  <si>
-    <t>宜春</t>
-  </si>
-  <si>
-    <t>惠州南</t>
-  </si>
-  <si>
-    <t>潮汕</t>
-  </si>
-  <si>
-    <t>泰安</t>
-  </si>
-  <si>
-    <t>曲阜东</t>
-  </si>
-  <si>
-    <t>临沂北</t>
-  </si>
-  <si>
-    <t>荆门西</t>
-  </si>
-  <si>
-    <t>杭州</t>
-  </si>
-  <si>
-    <t>咸阳北</t>
+    <t>湖州</t>
+  </si>
+  <si>
+    <t>宁波</t>
+  </si>
+  <si>
+    <t>芜湖</t>
+  </si>
+  <si>
+    <t>无锡东</t>
+  </si>
+  <si>
+    <t>100~200</t>
+  </si>
+  <si>
+    <t>苏州</t>
   </si>
 </sst>
 </file>
@@ -264,14 +1491,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -727,28 +1947,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -757,124 +1980,121 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1221,2071 +2441,3430 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B265"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:D429"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
+      <c r="A16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
+      <c r="A26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
+      <c r="A27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
+      <c r="A43" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
+      <c r="A52" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>8</v>
+        <v>101</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>20</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>21</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
+      <c r="A59" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>2</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>22</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>22</v>
+        <v>124</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
+      <c r="A66" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
+      <c r="A67" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>24</v>
+        <v>130</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>26</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>28</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>29</v>
+        <v>139</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>28</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>26</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>25</v>
+        <v>146</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>27</v>
+        <v>147</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>28</v>
+        <v>149</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>29</v>
+        <v>151</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>27</v>
+        <v>157</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>26</v>
+        <v>158</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>28</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="1" t="s">
-        <v>26</v>
+        <v>162</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
-        <v>27</v>
+        <v>165</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>28</v>
+        <v>166</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="1" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>29</v>
+        <v>168</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="1" t="s">
-        <v>27</v>
+        <v>169</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>28</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="1" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>30</v>
+        <v>172</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>29</v>
+        <v>174</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
-        <v>28</v>
+        <v>175</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>28</v>
+        <v>176</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>30</v>
+        <v>178</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="1" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>28</v>
+        <v>180</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="1" t="s">
-        <v>29</v>
+        <v>181</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>30</v>
+        <v>182</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="1" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
+      <c r="A96" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="1" t="s">
-        <v>31</v>
+        <v>187</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>32</v>
+        <v>188</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="1" t="s">
-        <v>31</v>
+        <v>189</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>33</v>
+        <v>190</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="1" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>34</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="1" t="s">
-        <v>31</v>
+        <v>193</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>35</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="1" t="s">
-        <v>31</v>
+        <v>195</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>22</v>
+        <v>196</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="1" t="s">
-        <v>31</v>
+        <v>197</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>33</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="D103" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>32</v>
+        <v>202</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="1" t="s">
-        <v>32</v>
+        <v>204</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="1" t="s">
-        <v>32</v>
+        <v>206</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>36</v>
+        <v>207</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="1" t="s">
-        <v>33</v>
+        <v>208</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>34</v>
+        <v>209</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="1" t="s">
-        <v>33</v>
+        <v>210</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>35</v>
+        <v>211</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="1" t="s">
-        <v>33</v>
+        <v>212</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>22</v>
+        <v>213</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="1" t="s">
-        <v>33</v>
+        <v>214</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>36</v>
+        <v>215</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="1" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>34</v>
+        <v>218</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>22</v>
+        <v>219</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>34</v>
+        <v>220</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>36</v>
+        <v>221</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>35</v>
+        <v>222</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>22</v>
+        <v>223</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="1" t="s">
-        <v>35</v>
+        <v>224</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>36</v>
+        <v>225</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="1" t="s">
-        <v>22</v>
+        <v>226</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>36</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="1"/>
-      <c r="B118" s="1"/>
+      <c r="A118" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="1" t="s">
-        <v>37</v>
+        <v>230</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>38</v>
+        <v>231</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="1" t="s">
-        <v>37</v>
+        <v>232</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>39</v>
+        <v>233</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="1" t="s">
-        <v>37</v>
+        <v>234</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>40</v>
+        <v>235</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="1" t="s">
-        <v>37</v>
+        <v>236</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>41</v>
+        <v>237</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="1" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>42</v>
+        <v>239</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="1" t="s">
-        <v>38</v>
+        <v>240</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>39</v>
+        <v>241</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="1" t="s">
-        <v>38</v>
+        <v>242</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>40</v>
+        <v>243</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="1" t="s">
-        <v>38</v>
+        <v>244</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>41</v>
+        <v>245</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="1" t="s">
-        <v>38</v>
+        <v>182</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>42</v>
+        <v>246</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="1" t="s">
-        <v>39</v>
+        <v>247</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="1" t="s">
-        <v>39</v>
+        <v>248</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>41</v>
+        <v>249</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="1" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>42</v>
+        <v>250</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="1" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>41</v>
+        <v>251</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="1" t="s">
-        <v>40</v>
+        <v>252</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>42</v>
+        <v>253</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="1" t="s">
-        <v>41</v>
+        <v>254</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>42</v>
+        <v>255</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="1"/>
-      <c r="B134" s="1"/>
+      <c r="A134" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="1" t="s">
-        <v>43</v>
+        <v>202</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="1" t="s">
-        <v>43</v>
+        <v>258</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>34</v>
+        <v>259</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="1" t="s">
-        <v>43</v>
+        <v>260</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>45</v>
+        <v>261</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="1" t="s">
-        <v>43</v>
+        <v>262</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>46</v>
+        <v>263</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="1" t="s">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>34</v>
+        <v>265</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="1" t="s">
-        <v>44</v>
+        <v>266</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>45</v>
+        <v>267</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="1" t="s">
-        <v>44</v>
+        <v>238</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>46</v>
+        <v>268</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="1" t="s">
-        <v>34</v>
+        <v>219</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>45</v>
+        <v>269</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="1" t="s">
-        <v>34</v>
+        <v>270</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>46</v>
+        <v>271</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="1" t="s">
-        <v>45</v>
+        <v>244</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>46</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="1"/>
-      <c r="B145" s="1"/>
+      <c r="A145" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="1" t="s">
-        <v>47</v>
+        <v>274</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>48</v>
+        <v>275</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="1" t="s">
-        <v>47</v>
+        <v>276</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>49</v>
+        <v>277</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="1" t="s">
-        <v>47</v>
+        <v>278</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="1" t="s">
-        <v>47</v>
+        <v>279</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>51</v>
+        <v>280</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="1" t="s">
-        <v>47</v>
+        <v>281</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>52</v>
+        <v>282</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="1" t="s">
-        <v>47</v>
+        <v>283</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="1" t="s">
-        <v>48</v>
+        <v>284</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>49</v>
+        <v>285</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="1" t="s">
-        <v>48</v>
+        <v>286</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>50</v>
+        <v>287</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="1" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>51</v>
+        <v>289</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="1" t="s">
-        <v>48</v>
+        <v>290</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>52</v>
+        <v>291</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="1" t="s">
-        <v>48</v>
+        <v>292</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>53</v>
+        <v>240</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="1" t="s">
-        <v>49</v>
+        <v>293</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>50</v>
+        <v>294</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="1" t="s">
-        <v>49</v>
+        <v>295</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>51</v>
+        <v>296</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="1" t="s">
-        <v>49</v>
+        <v>288</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>52</v>
+        <v>297</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="1" t="s">
-        <v>49</v>
+        <v>298</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>53</v>
+        <v>235</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="1" t="s">
-        <v>50</v>
+        <v>299</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>51</v>
+        <v>150</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="1" t="s">
-        <v>50</v>
+        <v>252</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>52</v>
+        <v>300</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="1" t="s">
-        <v>50</v>
+        <v>301</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>53</v>
+        <v>302</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="1" t="s">
-        <v>51</v>
+        <v>303</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="1" t="s">
-        <v>51</v>
+        <v>304</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>53</v>
+        <v>227</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="1" t="s">
-        <v>52</v>
+        <v>305</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>53</v>
+        <v>306</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="1"/>
-      <c r="B167" s="1"/>
+      <c r="A167" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="1"/>
-      <c r="B168" s="1"/>
+      <c r="A168" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="1" t="s">
-        <v>12</v>
+        <v>311</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>2</v>
+        <v>312</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="1" t="s">
-        <v>12</v>
+        <v>313</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>23</v>
+        <v>314</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="1" t="s">
-        <v>12</v>
+        <v>315</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>6</v>
+        <v>316</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="1" t="s">
-        <v>12</v>
+        <v>317</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>54</v>
+        <v>318</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="1" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>55</v>
+        <v>284</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="1" t="s">
-        <v>24</v>
+        <v>243</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>54</v>
+        <v>280</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="1" t="s">
-        <v>24</v>
+        <v>319</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>7</v>
+        <v>320</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="1" t="s">
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>56</v>
+        <v>321</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="1" t="s">
-        <v>24</v>
+        <v>322</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>20</v>
+        <v>323</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="1" t="s">
-        <v>28</v>
+        <v>294</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="1" t="s">
-        <v>28</v>
+        <v>325</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>54</v>
+        <v>326</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="1" t="s">
-        <v>28</v>
+        <v>327</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>7</v>
+        <v>328</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="1" t="s">
-        <v>28</v>
+        <v>329</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>56</v>
+        <v>321</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="1" t="s">
-        <v>28</v>
+        <v>222</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>20</v>
+        <v>330</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="1" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>23</v>
+        <v>332</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="1" t="s">
-        <v>57</v>
+        <v>255</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>15</v>
+        <v>333</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="1" t="s">
-        <v>57</v>
+        <v>334</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>22</v>
+        <v>335</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="1" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>30</v>
+        <v>336</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="1" t="s">
-        <v>57</v>
+        <v>337</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>20</v>
+        <v>338</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="1" t="s">
-        <v>57</v>
+        <v>339</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>58</v>
+        <v>283</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="1" t="s">
-        <v>30</v>
+        <v>340</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="1" t="s">
-        <v>59</v>
+        <v>341</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>22</v>
+        <v>342</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="1" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>60</v>
+        <v>343</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="1" t="s">
-        <v>29</v>
+        <v>344</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>61</v>
+        <v>345</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="1" t="s">
-        <v>62</v>
+        <v>346</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>61</v>
+        <v>347</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" s="1" t="s">
-        <v>57</v>
+        <v>348</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" s="1" t="s">
-        <v>49</v>
+        <v>349</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>61</v>
+        <v>350</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" s="1" t="s">
-        <v>47</v>
+        <v>351</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>61</v>
+        <v>332</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" s="1" t="s">
-        <v>63</v>
+        <v>352</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>61</v>
+        <v>353</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" s="1" t="s">
-        <v>64</v>
+        <v>316</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>10</v>
+        <v>127</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" s="1" t="s">
-        <v>65</v>
+        <v>286</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>2</v>
+        <v>354</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" s="1" t="s">
-        <v>65</v>
+        <v>270</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>66</v>
+        <v>355</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="1" t="s">
-        <v>65</v>
+        <v>356</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>41</v>
+        <v>288</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" s="1" t="s">
-        <v>65</v>
+        <v>357</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>60</v>
+        <v>358</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" s="1" t="s">
-        <v>65</v>
+        <v>359</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2">
-      <c r="A204" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>68</v>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="1"/>
+      <c r="B204" s="1"/>
+      <c r="D204" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" s="1" t="s">
-        <v>65</v>
+        <v>362</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>69</v>
+        <v>363</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" s="1" t="s">
-        <v>65</v>
+        <v>364</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>70</v>
+        <v>244</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" s="1" t="s">
-        <v>65</v>
+        <v>363</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>71</v>
+        <v>365</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" s="1" t="s">
-        <v>55</v>
+        <v>346</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>71</v>
+        <v>332</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" s="1" t="s">
-        <v>54</v>
+        <v>366</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>71</v>
+        <v>367</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" s="1" t="s">
-        <v>7</v>
+        <v>368</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>71</v>
+        <v>276</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" s="1" t="s">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>71</v>
+        <v>369</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" s="1" t="s">
-        <v>72</v>
+        <v>278</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>2</v>
+        <v>370</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" s="1" t="s">
-        <v>72</v>
+        <v>320</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>73</v>
+        <v>267</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" s="1" t="s">
-        <v>72</v>
+        <v>207</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>65</v>
+        <v>371</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" s="1" t="s">
-        <v>72</v>
+        <v>372</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>54</v>
+        <v>373</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" s="1" t="s">
-        <v>72</v>
+        <v>374</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>34</v>
+        <v>375</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" s="1" t="s">
-        <v>72</v>
+        <v>376</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>44</v>
+        <v>377</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" s="1" t="s">
-        <v>72</v>
+        <v>378</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>34</v>
+        <v>367</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" s="1" t="s">
-        <v>72</v>
+        <v>278</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>45</v>
+        <v>216</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" s="1" t="s">
-        <v>72</v>
+        <v>247</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>46</v>
+        <v>283</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" s="1" t="s">
-        <v>14</v>
+        <v>375</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>2</v>
+        <v>379</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" s="1" t="s">
-        <v>14</v>
+        <v>366</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>73</v>
+        <v>380</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" s="1" t="s">
-        <v>14</v>
+        <v>381</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>65</v>
+        <v>382</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" s="1" t="s">
-        <v>14</v>
+        <v>383</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>54</v>
+        <v>384</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" s="1" t="s">
-        <v>14</v>
+        <v>385</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>34</v>
+        <v>290</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" s="1" t="s">
-        <v>14</v>
+        <v>386</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" s="1" t="s">
-        <v>14</v>
+        <v>227</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" s="1" t="s">
-        <v>14</v>
+        <v>388</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>45</v>
+        <v>243</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" s="1" t="s">
-        <v>14</v>
+        <v>373</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>46</v>
+        <v>389</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" s="1" t="s">
-        <v>74</v>
+        <v>372</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>2</v>
+        <v>390</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" s="1" t="s">
-        <v>74</v>
+        <v>378</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>73</v>
+        <v>366</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" s="1" t="s">
-        <v>74</v>
+        <v>363</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>65</v>
+        <v>258</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" s="1" t="s">
-        <v>74</v>
+        <v>391</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>54</v>
+        <v>320</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" s="1" t="s">
-        <v>74</v>
+        <v>392</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>34</v>
+        <v>393</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" s="1" t="s">
-        <v>74</v>
+        <v>394</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>44</v>
+        <v>395</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" s="1" t="s">
-        <v>74</v>
+        <v>396</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>34</v>
+        <v>397</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" s="1" t="s">
-        <v>74</v>
+        <v>398</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>45</v>
+        <v>399</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" s="1" t="s">
-        <v>74</v>
+        <v>400</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" s="1" t="s">
-        <v>31</v>
+        <v>401</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>25</v>
+        <v>402</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="1" t="s">
-        <v>31</v>
+        <v>328</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>26</v>
+        <v>392</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" s="1" t="s">
-        <v>31</v>
+        <v>403</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>27</v>
+        <v>404</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" s="1" t="s">
-        <v>31</v>
+        <v>405</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>28</v>
+        <v>406</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" s="1" t="s">
-        <v>31</v>
+        <v>407</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>29</v>
+        <v>277</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" s="1" t="s">
-        <v>31</v>
+        <v>228</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>28</v>
+        <v>402</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" s="1" t="s">
-        <v>31</v>
+        <v>375</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>30</v>
+        <v>251</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" s="1" t="s">
-        <v>33</v>
+        <v>244</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>25</v>
+        <v>182</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" s="1" t="s">
-        <v>33</v>
+        <v>408</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>26</v>
+        <v>409</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" s="1" t="s">
-        <v>33</v>
+        <v>410</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>27</v>
+        <v>411</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" s="1" t="s">
-        <v>33</v>
+        <v>412</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>28</v>
+        <v>413</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" s="1" t="s">
-        <v>33</v>
+        <v>243</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>29</v>
+        <v>345</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" s="1" t="s">
-        <v>33</v>
+        <v>320</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>28</v>
+        <v>238</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" s="1" t="s">
-        <v>33</v>
+        <v>327</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>30</v>
+        <v>414</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" s="1" t="s">
-        <v>25</v>
+        <v>397</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>37</v>
+        <v>415</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" s="1" t="s">
-        <v>26</v>
+        <v>416</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>37</v>
+        <v>320</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" s="1" t="s">
-        <v>27</v>
+        <v>217</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" s="1" t="s">
-        <v>28</v>
+        <v>417</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>37</v>
+        <v>418</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" s="1" t="s">
-        <v>29</v>
+        <v>419</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>37</v>
+        <v>420</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="1" t="s">
-        <v>28</v>
+        <v>421</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>37</v>
+        <v>422</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" s="1" t="s">
-        <v>30</v>
+        <v>423</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>37</v>
+        <v>405</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" s="1" t="s">
-        <v>44</v>
+        <v>424</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>26</v>
+        <v>264</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" s="1" t="s">
-        <v>44</v>
+        <v>228</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>27</v>
+        <v>391</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" s="1" t="s">
-        <v>44</v>
+        <v>391</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>28</v>
+        <v>425</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" s="1" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>29</v>
+        <v>426</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" s="1" t="s">
-        <v>44</v>
+        <v>427</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>28</v>
+        <v>182</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" s="1" t="s">
-        <v>44</v>
+        <v>428</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>30</v>
+        <v>429</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" t="s">
+        <v>430</v>
+      </c>
+      <c r="B266" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" t="s">
+        <v>432</v>
+      </c>
+      <c r="B267" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" t="s">
+        <v>300</v>
+      </c>
+      <c r="B268" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" t="s">
+        <v>391</v>
+      </c>
+      <c r="B269" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" t="s">
+        <v>435</v>
+      </c>
+      <c r="B270" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" t="s">
+        <v>437</v>
+      </c>
+      <c r="B271" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" t="s">
+        <v>428</v>
+      </c>
+      <c r="B272" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" t="s">
+        <v>394</v>
+      </c>
+      <c r="B273" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" t="s">
+        <v>437</v>
+      </c>
+      <c r="B274" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" t="s">
+        <v>394</v>
+      </c>
+      <c r="B275" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" t="s">
+        <v>417</v>
+      </c>
+      <c r="B276" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" t="s">
+        <v>440</v>
+      </c>
+      <c r="B277" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" t="s">
+        <v>442</v>
+      </c>
+      <c r="B278" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" t="s">
+        <v>399</v>
+      </c>
+      <c r="B279" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" t="s">
+        <v>443</v>
+      </c>
+      <c r="B280" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" t="s">
+        <v>372</v>
+      </c>
+      <c r="B281" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" t="s">
+        <v>265</v>
+      </c>
+      <c r="B282" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" t="s">
+        <v>407</v>
+      </c>
+      <c r="B283" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" t="s">
+        <v>428</v>
+      </c>
+      <c r="B284" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" t="s">
+        <v>216</v>
+      </c>
+      <c r="B285" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" t="s">
+        <v>449</v>
+      </c>
+      <c r="B286" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" t="s">
+        <v>450</v>
+      </c>
+      <c r="B287" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" t="s">
+        <v>452</v>
+      </c>
+      <c r="B288" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" t="s">
+        <v>264</v>
+      </c>
+      <c r="B289" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" t="s">
+        <v>366</v>
+      </c>
+      <c r="B290" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" t="s">
+        <v>283</v>
+      </c>
+      <c r="B291" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" t="s">
+        <v>383</v>
+      </c>
+      <c r="B292" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" t="s">
+        <v>222</v>
+      </c>
+      <c r="B293" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" t="s">
+        <v>454</v>
+      </c>
+      <c r="B294" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" t="s">
+        <v>455</v>
+      </c>
+      <c r="B295" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" t="s">
+        <v>456</v>
+      </c>
+      <c r="B296" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" t="s">
+        <v>289</v>
+      </c>
+      <c r="B297" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" t="s">
+        <v>60</v>
+      </c>
+      <c r="B298" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" t="s">
+        <v>294</v>
+      </c>
+      <c r="B299" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" t="s">
+        <v>356</v>
+      </c>
+      <c r="B300" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" t="s">
+        <v>383</v>
+      </c>
+      <c r="B301" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" t="s">
+        <v>454</v>
+      </c>
+      <c r="B302" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" t="s">
+        <v>461</v>
+      </c>
+      <c r="B303" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" t="s">
+        <v>364</v>
+      </c>
+      <c r="B304" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="305" spans="4:4">
+      <c r="D305" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" t="s">
+        <v>464</v>
+      </c>
+      <c r="B306" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" t="s">
+        <v>244</v>
+      </c>
+      <c r="B307" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" t="s">
+        <v>375</v>
+      </c>
+      <c r="B308" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" t="s">
+        <v>466</v>
+      </c>
+      <c r="B309" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" t="s">
+        <v>182</v>
+      </c>
+      <c r="B310" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" t="s">
+        <v>320</v>
+      </c>
+      <c r="B311" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" t="s">
+        <v>412</v>
+      </c>
+      <c r="B312" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" t="s">
+        <v>468</v>
+      </c>
+      <c r="B313" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" t="s">
+        <v>452</v>
+      </c>
+      <c r="B314" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" t="s">
+        <v>289</v>
+      </c>
+      <c r="B315" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" t="s">
+        <v>457</v>
+      </c>
+      <c r="B316" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" t="s">
+        <v>244</v>
+      </c>
+      <c r="B317" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" t="s">
+        <v>452</v>
+      </c>
+      <c r="B318" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" t="s">
+        <v>364</v>
+      </c>
+      <c r="B319" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" t="s">
+        <v>232</v>
+      </c>
+      <c r="B320" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" t="s">
+        <v>367</v>
+      </c>
+      <c r="B321" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" t="s">
+        <v>283</v>
+      </c>
+      <c r="B322" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" t="s">
+        <v>466</v>
+      </c>
+      <c r="B323" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" t="s">
+        <v>368</v>
+      </c>
+      <c r="B324" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" t="s">
+        <v>332</v>
+      </c>
+      <c r="B325" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" t="s">
+        <v>452</v>
+      </c>
+      <c r="B326" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" t="s">
+        <v>101</v>
+      </c>
+      <c r="B327" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" t="s">
+        <v>375</v>
+      </c>
+      <c r="B328" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" t="s">
+        <v>469</v>
+      </c>
+      <c r="B329" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" t="s">
+        <v>392</v>
+      </c>
+      <c r="B330" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" t="s">
+        <v>203</v>
+      </c>
+      <c r="B331" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" t="s">
+        <v>293</v>
+      </c>
+      <c r="B332" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" t="s">
+        <v>332</v>
+      </c>
+      <c r="B333" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" t="s">
+        <v>316</v>
+      </c>
+      <c r="B334" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" t="s">
+        <v>453</v>
+      </c>
+      <c r="B335" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" t="s">
+        <v>405</v>
+      </c>
+      <c r="B336" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" t="s">
+        <v>264</v>
+      </c>
+      <c r="B337" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" t="s">
+        <v>366</v>
+      </c>
+      <c r="B338" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" t="s">
+        <v>411</v>
+      </c>
+      <c r="B339" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" t="s">
+        <v>472</v>
+      </c>
+      <c r="B340" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" t="s">
+        <v>432</v>
+      </c>
+      <c r="B341" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" t="s">
+        <v>381</v>
+      </c>
+      <c r="B342" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" t="s">
+        <v>213</v>
+      </c>
+      <c r="B343" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" t="s">
+        <v>472</v>
+      </c>
+      <c r="B344" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" t="s">
+        <v>264</v>
+      </c>
+      <c r="B345" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" t="s">
+        <v>366</v>
+      </c>
+      <c r="B346" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" t="s">
+        <v>394</v>
+      </c>
+      <c r="B347" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" t="s">
+        <v>378</v>
+      </c>
+      <c r="B348" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" t="s">
+        <v>202</v>
+      </c>
+      <c r="B349" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" t="s">
+        <v>364</v>
+      </c>
+      <c r="B350" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" t="s">
+        <v>163</v>
+      </c>
+      <c r="B351" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" t="s">
+        <v>366</v>
+      </c>
+      <c r="B352" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" t="s">
+        <v>475</v>
+      </c>
+      <c r="B353" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" t="s">
+        <v>283</v>
+      </c>
+      <c r="B354" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" t="s">
+        <v>394</v>
+      </c>
+      <c r="B355" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="356" spans="4:4">
+      <c r="D356" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" t="s">
+        <v>435</v>
+      </c>
+      <c r="B357" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" t="s">
+        <v>477</v>
+      </c>
+      <c r="B358" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" t="s">
+        <v>294</v>
+      </c>
+      <c r="B359" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" t="s">
+        <v>464</v>
+      </c>
+      <c r="B360" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" t="s">
+        <v>394</v>
+      </c>
+      <c r="B361" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" t="s">
+        <v>368</v>
+      </c>
+      <c r="B362" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" t="s">
+        <v>477</v>
+      </c>
+      <c r="B363" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" t="s">
+        <v>472</v>
+      </c>
+      <c r="B364" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" t="s">
+        <v>472</v>
+      </c>
+      <c r="B365" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" t="s">
+        <v>375</v>
+      </c>
+      <c r="B366" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" t="s">
+        <v>244</v>
+      </c>
+      <c r="B367" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" t="s">
+        <v>372</v>
+      </c>
+      <c r="B368" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" t="s">
+        <v>392</v>
+      </c>
+      <c r="B369" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" t="s">
+        <v>364</v>
+      </c>
+      <c r="B370" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" t="s">
+        <v>227</v>
+      </c>
+      <c r="B371" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" t="s">
+        <v>453</v>
+      </c>
+      <c r="B372" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" t="s">
+        <v>418</v>
+      </c>
+      <c r="B373" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" t="s">
+        <v>394</v>
+      </c>
+      <c r="B374" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" t="s">
+        <v>469</v>
+      </c>
+      <c r="B375" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" t="s">
+        <v>286</v>
+      </c>
+      <c r="B376" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" t="s">
+        <v>478</v>
+      </c>
+      <c r="B377" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" t="s">
+        <v>366</v>
+      </c>
+      <c r="B378" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" t="s">
+        <v>464</v>
+      </c>
+      <c r="B379" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" t="s">
+        <v>480</v>
+      </c>
+      <c r="B380" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" t="s">
+        <v>367</v>
+      </c>
+      <c r="B381" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" t="s">
+        <v>469</v>
+      </c>
+      <c r="B382" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" t="s">
+        <v>381</v>
+      </c>
+      <c r="B383" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" t="s">
+        <v>163</v>
+      </c>
+      <c r="B384" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" t="s">
+        <v>435</v>
+      </c>
+      <c r="B385" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" t="s">
+        <v>381</v>
+      </c>
+      <c r="B386" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" t="s">
+        <v>182</v>
+      </c>
+      <c r="B387" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" t="s">
+        <v>464</v>
+      </c>
+      <c r="B388" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" t="s">
+        <v>227</v>
+      </c>
+      <c r="B389" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" t="s">
+        <v>440</v>
+      </c>
+      <c r="B390" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" t="s">
+        <v>332</v>
+      </c>
+      <c r="B391" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" t="s">
+        <v>366</v>
+      </c>
+      <c r="B392" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" t="s">
+        <v>392</v>
+      </c>
+      <c r="B393" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" t="s">
+        <v>213</v>
+      </c>
+      <c r="B394" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" t="s">
+        <v>375</v>
+      </c>
+      <c r="B395" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" t="s">
+        <v>244</v>
+      </c>
+      <c r="B396" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" t="s">
+        <v>367</v>
+      </c>
+      <c r="B397" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" t="s">
+        <v>264</v>
+      </c>
+      <c r="B398" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" t="s">
+        <v>207</v>
+      </c>
+      <c r="B399" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" t="s">
+        <v>294</v>
+      </c>
+      <c r="B400" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" t="s">
+        <v>244</v>
+      </c>
+      <c r="B401" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" t="s">
+        <v>227</v>
+      </c>
+      <c r="B402" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" t="s">
+        <v>381</v>
+      </c>
+      <c r="B403" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" t="s">
+        <v>294</v>
+      </c>
+      <c r="B404" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" t="s">
+        <v>294</v>
+      </c>
+      <c r="B405" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" t="s">
+        <v>464</v>
+      </c>
+      <c r="B406" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="407" spans="4:4">
+      <c r="D407" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" t="s">
+        <v>227</v>
+      </c>
+      <c r="B408" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" t="s">
+        <v>394</v>
+      </c>
+      <c r="B409" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" t="s">
+        <v>264</v>
+      </c>
+      <c r="B410" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" t="s">
+        <v>332</v>
+      </c>
+      <c r="B411" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" t="s">
+        <v>381</v>
+      </c>
+      <c r="B412" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" t="s">
+        <v>294</v>
+      </c>
+      <c r="B413" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" t="s">
+        <v>64</v>
+      </c>
+      <c r="B414" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" t="s">
+        <v>294</v>
+      </c>
+      <c r="B415" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" t="s">
+        <v>182</v>
+      </c>
+      <c r="B416" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" t="s">
+        <v>381</v>
+      </c>
+      <c r="B417" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" t="s">
+        <v>64</v>
+      </c>
+      <c r="B418" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" t="s">
+        <v>284</v>
+      </c>
+      <c r="B419" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" t="s">
+        <v>381</v>
+      </c>
+      <c r="B420" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" t="s">
+        <v>392</v>
+      </c>
+      <c r="B421" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" t="s">
+        <v>244</v>
+      </c>
+      <c r="B422" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" t="s">
+        <v>286</v>
+      </c>
+      <c r="B423" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" t="s">
+        <v>227</v>
+      </c>
+      <c r="B424" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" t="s">
+        <v>394</v>
+      </c>
+      <c r="B425" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" t="s">
+        <v>366</v>
+      </c>
+      <c r="B426" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" t="s">
+        <v>483</v>
+      </c>
+      <c r="B427" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" t="s">
+        <v>477</v>
+      </c>
+      <c r="B428" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" t="s">
+        <v>477</v>
+      </c>
+      <c r="B429" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>
